--- a/src/test/resources/TEST_DATA/TransfersPageData.xlsx
+++ b/src/test/resources/TEST_DATA/TransfersPageData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="OwnAccountTransferData" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>errorMsg1</t>
   </si>
@@ -114,6 +114,9 @@
     <t xml:space="preserve">SAMPATH BANK PLC - COMPANY NO PQ 144</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>errCreditCardNumberRequired</t>
   </si>
   <si>
@@ -189,7 +192,10 @@
     <t xml:space="preserve">Allowed Maximum transaction amount is 30000.00</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insufficient funds in the selected account</t>
   </si>
 </sst>
 </file>
@@ -238,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -254,6 +260,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -939,8 +946,8 @@
       <c r="K2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="3">
-        <v>2</v>
+      <c r="L2" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -957,47 +964,48 @@
   <cols>
     <col customWidth="1" min="8" max="8" width="24.7109375"/>
     <col customWidth="1" min="9" max="9" width="33.28125"/>
+    <col customWidth="1" min="19" max="19" width="24.8515625"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="57">
-      <c r="A1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="8" t="s">
         <v>32</v>
       </c>
+      <c r="B1" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="C1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="8" t="s">
         <v>40</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>23</v>
@@ -1006,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -1015,7 +1023,7 @@
         <v>2</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>10</v>
@@ -1023,40 +1031,40 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="114">
       <c r="A2" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M2" s="5">
         <v>30001</v>
@@ -1068,16 +1076,16 @@
         <v>17</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>501</v>
+        <v>56</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="R2" s="5">
         <v>0</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>18</v>

--- a/src/test/resources/TEST_DATA/TransfersPageData.xlsx
+++ b/src/test/resources/TEST_DATA/TransfersPageData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="OwnAccountTransferData" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>errorMsg1</t>
   </si>
@@ -102,6 +102,9 @@
 Insufficient funds in the selected account</t>
   </si>
   <si>
+    <t xml:space="preserve">Allowed Maximum transaction amount is 50,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
+  </si>
+  <si>
     <t>002550040541</t>
   </si>
   <si>
@@ -189,7 +192,7 @@
     <t>BADULLA</t>
   </si>
   <si>
-    <t xml:space="preserve">Allowed Maximum transaction amount is 30000.00</t>
+    <t xml:space="preserve">Allowed Maximum transaction amount is 30,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
   </si>
   <si>
     <t>501</t>
@@ -260,12 +263,14 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,7 +874,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="23.421875"/>
     <col customWidth="1" min="2" max="2" width="11.421875"/>
-    <col customWidth="1" min="5" max="5" width="24.8515625"/>
+    <col customWidth="1" min="5" max="5" width="57.7109375"/>
     <col customWidth="1" min="6" max="6" width="20.421875"/>
     <col bestFit="1" min="7" max="7" width="10.7109375"/>
   </cols>
@@ -926,10 +931,10 @@
         <v>18</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>16</v>
@@ -938,16 +943,16 @@
         <v>17</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="7" t="s">
         <v>31</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -968,44 +973,44 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="57">
-      <c r="A1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="B1" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="9" t="s">
         <v>41</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>23</v>
@@ -1014,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -1023,7 +1028,7 @@
         <v>2</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>10</v>
@@ -1031,61 +1036,61 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="114">
       <c r="A2" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M2" s="5">
         <v>30001</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>56</v>
+      <c r="P2" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R2" s="5">
         <v>0</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>18</v>

--- a/src/test/resources/TEST_DATA/TransfersPageData.xlsx
+++ b/src/test/resources/TEST_DATA/TransfersPageData.xlsx
@@ -165,7 +165,7 @@
     <t xml:space="preserve">Credit Card Number/CAN is required</t>
   </si>
   <si>
-    <t xml:space="preserve">Re-enter Credit Card Number/CAN is required</t>
+    <t xml:space="preserve">Re-enter credit card number / CAN is required</t>
   </si>
   <si>
     <t xml:space="preserve">Name On Card is required</t>
@@ -1034,11 +1034,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="114">
+    <row r="2" s="2" customFormat="1" ht="327.75">
       <c r="A2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1080,7 +1080,7 @@
       <c r="O2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="5" t="s">
         <v>57</v>
       </c>
       <c r="Q2" s="5" t="s">

--- a/src/test/resources/TEST_DATA/TransfersPageData.xlsx
+++ b/src/test/resources/TEST_DATA/TransfersPageData.xlsx
@@ -1,31 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sampath_QA\Automation\svr4-api-automations\svr4-api-automations\src\test\resources\TEST_DATA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A16196-CCDB-4F48-A939-40326ED0DC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="OwnAccountTransferData" sheetId="1" r:id="rId1"/>
-    <sheet name="OtherAccountTransfersData" sheetId="2" r:id="rId2"/>
-    <sheet name="OwnBankTransactions" sheetId="3" r:id="rId3"/>
-    <sheet name="OtherCreditCardTransferData" sheetId="4" r:id="rId4"/>
-    <sheet name="MobileCashData" sheetId="5" r:id="rId5"/>
-    <sheet name="StaffAccountTransfersData" sheetId="6" r:id="rId6"/>
+    <sheet name="OwnAccountTransferData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OtherAccountTransfersData" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="OwnBankTransactions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="OtherCreditCardTransferData" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MobileCashData" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="StaffAccountTransfersData" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>errorMsg1</t>
   </si>
@@ -60,31 +56,28 @@
     <t>errMinimumTransferAmount</t>
   </si>
   <si>
-    <t>To Account is required</t>
-  </si>
-  <si>
-    <t>Amount is required</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>500001</t>
-  </si>
-  <si>
-    <t>Limit exceeded, use mobile app for higher limits</t>
-  </si>
-  <si>
-    <t>Allowed Maximum transaction amount is LKR 50000.00</t>
+    <t xml:space="preserve">To Account is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed Minimum transaction amount is LKR 15.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed Maximum transaction amount is LKR 50000.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0167 5100 0152</t>
   </si>
   <si>
     <t>51</t>
   </si>
   <si>
-    <t>One-time Transaction</t>
-  </si>
-  <si>
-    <t>Minimum transfer amount must be greater than LKR 0.00</t>
+    <t xml:space="preserve">One-time Transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum transfer amount must be greater than LKR 0.00</t>
   </si>
   <si>
     <t>errorMsgInsufficientFunds</t>
@@ -111,23 +104,29 @@
     <t>actualTransactionAmount</t>
   </si>
   <si>
-    <t>actualTransactionAmount
+    <t xml:space="preserve">actualTransactionAmount
 Insufficient funds in the selected account</t>
   </si>
   <si>
-    <t>Minimum transfer amount must be greater than Rs.0</t>
+    <t xml:space="preserve">Minimum transfer amount must be greater than Rs.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed Maximum transaction amount is LKR 50,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
+  </si>
+  <si>
+    <t>002550040541</t>
   </si>
   <si>
     <t>Baabu</t>
   </si>
   <si>
-    <t>Profit Income</t>
-  </si>
-  <si>
-    <t>TEST BANK B</t>
-  </si>
-  <si>
-    <t>CITY OFFICE</t>
+    <t xml:space="preserve">Profit Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST BANK B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CITY OFFICE</t>
   </si>
   <si>
     <t>500</t>
@@ -136,13 +135,10 @@
     <t>bankNameTwo</t>
   </si>
   <si>
-    <t>Allowed Maximum transaction amount is LKR 50,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
-  </si>
-  <si>
-    <t>SAMPATH BANK PLC - COMPANY NO PQ 144</t>
-  </si>
-  <si>
-    <t>NDB BANK</t>
+    <t xml:space="preserve">SAMPATH BANK PLC - COMPANY NO PQ 144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDB BANK</t>
   </si>
   <si>
     <t>2</t>
@@ -190,22 +186,22 @@
     <t>errInsufficientfunds</t>
   </si>
   <si>
-    <t>Credit Card Number/CAN is required</t>
-  </si>
-  <si>
-    <t>Re-enter credit card number / CAN is required</t>
-  </si>
-  <si>
-    <t>Name On Card is required</t>
-  </si>
-  <si>
-    <t>Bank is required</t>
-  </si>
-  <si>
-    <t>Select Purpose</t>
-  </si>
-  <si>
-    <t>Beneficiary Remark is required</t>
+    <t xml:space="preserve">Credit Card Number/CAN is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-enter credit card number / CAN is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name On Card is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beneficiary Remark is required</t>
   </si>
   <si>
     <t>376657973920377</t>
@@ -214,19 +210,19 @@
     <t>Supun</t>
   </si>
   <si>
-    <t>NATIONS TRUST BANK</t>
+    <t xml:space="preserve">NATIONS TRUST BANK</t>
   </si>
   <si>
     <t>BADULLA</t>
   </si>
   <si>
-    <t>Allowed Maximum transaction amount is LKR 30,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
+    <t xml:space="preserve">Allowed Maximum transaction amount is LKR 30,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
   </si>
   <si>
     <t>501</t>
   </si>
   <si>
-    <t>Insufficient funds in the selected account</t>
+    <t xml:space="preserve">Insufficient funds in the selected account</t>
   </si>
   <si>
     <t>errNICNumberRequired</t>
@@ -256,25 +252,25 @@
     <t>maxAmountInHundred</t>
   </si>
   <si>
-    <t>Receiver's NIC Number is required</t>
-  </si>
-  <si>
-    <t>Receiver's Mobile Number is required</t>
-  </si>
-  <si>
-    <t>Re-enter Receiver's Mobile Number is required</t>
-  </si>
-  <si>
-    <t>Receiver's Name is required</t>
-  </si>
-  <si>
-    <t>Mobile Cash Amount is required</t>
-  </si>
-  <si>
-    <t>Remark is required</t>
-  </si>
-  <si>
-    <t>Amount must be in multiples of Rs.100</t>
+    <t xml:space="preserve">Receiver's NIC Number is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver's Mobile Number is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-enter Receiver's Mobile Number is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver's Name is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Cash Amount is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remark is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount must be in multiples of Rs.100</t>
   </si>
   <si>
     <t>654465465465</t>
@@ -286,7 +282,7 @@
     <t>Trump</t>
   </si>
   <si>
-    <t>Allowed Maximum transaction amount is LKR 10,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
+    <t xml:space="preserve">Allowed Maximum transaction amount is LKR 10,000.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
   </si>
   <si>
     <t>800</t>
@@ -295,7 +291,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>Allowed Minimum transaction amount is LKR 800.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
+    <t xml:space="preserve">Allowed Minimum transaction amount is LKR 800.00 If you need to adjust your limit for specific requirements, please send a Vishwa request to your Branch Manager.</t>
   </si>
   <si>
     <t>10100</t>
@@ -304,66 +300,44 @@
     <t>errorMsg</t>
   </si>
   <si>
-    <t>Please Enter Correct Account Number</t>
+    <t xml:space="preserve">Please Enter Correct Account Number</t>
   </si>
   <si>
     <t>100105233673</t>
   </si>
   <si>
     <t>Kayne</t>
-  </si>
-  <si>
-    <t>1025 5203 6877</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12.000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <color rgb="FF067D17"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
+      <color indexed="64"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FFE4E2E3"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -376,43 +350,46 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="13">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,15 +400,295 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -634,30 +891,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="5" max="5" width="44.5546875" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="27.7109375"/>
+    <col customWidth="1" min="2" max="2" width="18.57421875"/>
+    <col customWidth="1" min="3" max="3" width="13.421875"/>
+    <col customWidth="1" min="4" max="4" width="12.140625"/>
+    <col customWidth="1" min="5" max="5" width="44.57421875"/>
+    <col customWidth="1" min="6" max="6" width="17.00390625"/>
+    <col customWidth="1" min="7" max="7" width="12.140625"/>
+    <col customWidth="1" min="9" max="9" width="15.00390625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" ht="57">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -672,7 +927,7 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -681,75 +936,76 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="99.75">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3">
+        <v>50001</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="J2" s="5">
         <v>0</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="57.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1"/>
+    <col customWidth="1" min="1" max="1" width="23.421875"/>
+    <col customWidth="1" min="2" max="2" width="11.421875"/>
+    <col customWidth="1" min="5" max="5" width="57.7109375"/>
+    <col customWidth="1" min="6" max="6" width="20.421875"/>
+    <col bestFit="1" min="7" max="7" width="10.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" ht="14.25">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -767,240 +1023,239 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>26</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" ht="42.75">
+      <c r="A2" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>500000</v>
+        <v>50001</v>
       </c>
       <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F6" s="9"/>
+      <c r="M2" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" ht="14.25">
+      <c r="A1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="L1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="114">
+      <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7">
+        <v>50001</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>50000</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="8" max="8" width="24.6640625" customWidth="1"/>
-    <col min="9" max="9" width="33.33203125" customWidth="1"/>
-    <col min="19" max="19" width="24.88671875" customWidth="1"/>
+    <col customWidth="1" min="8" max="8" width="24.7109375"/>
+    <col customWidth="1" min="9" max="9" width="33.28125"/>
+    <col customWidth="1" min="19" max="19" width="24.8515625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="66.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="2" customFormat="1" ht="57">
+      <c r="A1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="2" s="2" customFormat="1" ht="327.75">
       <c r="A2" s="5" t="s">
         <v>54</v>
       </c>
@@ -1041,10 +1296,10 @@
         <v>30001</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>64</v>
@@ -1059,216 +1314,219 @@
         <v>66</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" style="2" bestFit="1"/>
-    <col min="2" max="2" width="23.88671875" style="2" bestFit="1"/>
-    <col min="3" max="3" width="30.5546875" style="2" bestFit="1"/>
-    <col min="4" max="4" width="15.88671875" style="2" bestFit="1"/>
-    <col min="5" max="5" width="28.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18" style="2" bestFit="1"/>
-    <col min="7" max="7" width="26.6640625" style="2" bestFit="1"/>
-    <col min="8" max="8" width="29.33203125" style="2" bestFit="1"/>
-    <col min="9" max="9" width="20.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2" bestFit="1"/>
-    <col min="11" max="11" width="5.5546875" style="2" bestFit="1"/>
-    <col min="12" max="12" width="9.109375" style="2"/>
-    <col min="13" max="13" width="143.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.109375" style="2"/>
-    <col min="15" max="15" width="11" style="2" bestFit="1"/>
-    <col min="16" max="16" width="17.44140625" style="2" bestFit="1"/>
-    <col min="17" max="17" width="25.5546875" style="2" bestFit="1"/>
-    <col min="18" max="16384" width="9.109375" style="2"/>
+    <col bestFit="1" min="1" max="1" style="3" width="20.8515625"/>
+    <col bestFit="1" min="2" max="2" style="3" width="23.8515625"/>
+    <col bestFit="1" min="3" max="3" style="3" width="30.57421875"/>
+    <col bestFit="1" min="4" max="4" style="3" width="15.8515625"/>
+    <col customWidth="1" min="5" max="5" style="3" width="28.140625"/>
+    <col bestFit="1" min="6" max="6" style="3" width="18.00390625"/>
+    <col bestFit="1" min="7" max="7" style="3" width="26.7109375"/>
+    <col bestFit="1" min="8" max="8" style="3" width="29.28125"/>
+    <col bestFit="1" min="9" max="9" style="3" width="10.140625"/>
+    <col bestFit="1" min="10" max="10" style="3" width="9.00390625"/>
+    <col bestFit="1" min="11" max="11" style="3" width="5.57421875"/>
+    <col min="12" max="12" style="3" width="9.140625"/>
+    <col bestFit="1" min="13" max="13" style="3" width="30.421875"/>
+    <col min="14" max="14" style="3" width="9.140625"/>
+    <col bestFit="1" min="15" max="15" style="3" width="11.00390625"/>
+    <col bestFit="1" min="16" max="16" style="3" width="17.421875"/>
+    <col bestFit="1" min="17" max="17" style="3" width="25.57421875"/>
+    <col min="18" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="14.25">
+      <c r="A1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="S1" s="3"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="14.25">
+      <c r="A2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="L2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>90</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="2"/>
-    <col min="2" max="2" width="37" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1">
+      <c r="A1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2">
+      <c r="A2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>